--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N61_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N61_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.618391045519942</v>
+        <v>1.562988544896991</v>
       </c>
       <c r="D2" t="n">
-        <v>24.92837211542294</v>
+        <v>4.050860468756229</v>
       </c>
       <c r="E2" t="n">
-        <v>44.56026747487802</v>
+        <v>7.241043464667679</v>
       </c>
       <c r="F2" t="n">
-        <v>3.650695648021705</v>
+        <v>0.5932380428035273</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>98.73892599527598</v>
+        <v>16.04507547423235</v>
       </c>
       <c r="D3" t="n">
-        <v>17.62698081937953</v>
+        <v>2.864384383149174</v>
       </c>
       <c r="E3" t="n">
-        <v>44.56026747487802</v>
+        <v>7.241043464667679</v>
       </c>
       <c r="F3" t="n">
-        <v>3.650695648021705</v>
+        <v>0.5932380428035273</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
